--- a/pinout.xlsx
+++ b/pinout.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
   <si>
     <t>3V3</t>
   </si>
@@ -176,14 +176,35 @@
     <t>SC05-H2S</t>
   </si>
   <si>
-    <t>SCD40/41 CO2</t>
+    <t>HEAT_PWM</t>
+  </si>
+  <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <t>MQ-7 (CO)</t>
+  </si>
+  <si>
+    <t>DHT22</t>
+  </si>
+  <si>
+    <t>SDA</t>
+  </si>
+  <si>
+    <t>USB</t>
+  </si>
+  <si>
+    <t>SCD40/CO2</t>
+  </si>
+  <si>
+    <t>ZC13 CH4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,8 +212,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -220,6 +248,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -277,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -285,32 +325,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C6:I27"/>
+  <dimension ref="C6:I29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
@@ -602,125 +657,144 @@
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E6" s="2" t="s">
+    <row r="6" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="E6" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E7" s="2" t="s">
+    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="E7" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="11"/>
       <c r="G7" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
       <c r="E8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="7" t="s">
+      <c r="F8" s="11"/>
+      <c r="G8" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C9" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="11"/>
+      <c r="G9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="I9" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C10" s="12"/>
+      <c r="D10" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="9" t="s">
+      <c r="F10" s="11"/>
+      <c r="G10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
       <c r="E11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="11"/>
+      <c r="G11" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="11"/>
       <c r="G12" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:9" x14ac:dyDescent="0.25">
       <c r="E13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="11"/>
       <c r="G13" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="11"/>
       <c r="G14" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
       <c r="E15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="11"/>
       <c r="G15" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:9" x14ac:dyDescent="0.25">
       <c r="E16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="11"/>
       <c r="G16" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C17" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="D17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="11"/>
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
@@ -729,7 +803,7 @@
       <c r="E18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="2" t="s">
         <v>20</v>
       </c>
@@ -738,70 +812,73 @@
       <c r="E19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="D20" s="6" t="s">
+      <c r="C20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="9" t="s">
+      <c r="F21" s="11"/>
+      <c r="G21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="12" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C22" s="5"/>
-      <c r="D22" s="9" t="s">
+      <c r="C22" s="12"/>
+      <c r="D22" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4" t="s">
+      <c r="F22" s="11"/>
+      <c r="G22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I22" s="5"/>
+      <c r="I22" s="12"/>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C23" s="5"/>
-      <c r="D23" s="4" t="s">
+      <c r="C23" s="12"/>
+      <c r="D23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="2" t="s">
         <v>19</v>
       </c>
@@ -810,7 +887,7 @@
       <c r="E24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="2" t="s">
         <v>18</v>
       </c>
@@ -819,36 +896,43 @@
       <c r="E25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="2" t="s">
+      <c r="F26" s="11"/>
+      <c r="G26" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="2" t="s">
+      <c r="F27" s="11"/>
+      <c r="G27" s="14" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="F29" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="F6:F27"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="I9:I10"/>
+    <mergeCell ref="C9:C10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/pinout.xlsx
+++ b/pinout.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
   <si>
     <t>3V3</t>
   </si>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t>ZC13 CH4</t>
+  </si>
+  <si>
+    <t>RGB</t>
+  </si>
+  <si>
+    <t>MQ-137(NH3)</t>
   </si>
 </sst>
 </file>
@@ -235,12 +241,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -260,6 +260,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -331,22 +337,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -355,17 +358,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -647,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C6:I29"/>
+  <dimension ref="C6:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
@@ -658,21 +676,21 @@
   </cols>
   <sheetData>
     <row r="6" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="11"/>
+      <c r="F7" s="10"/>
       <c r="G7" s="2" t="s">
         <v>31</v>
       </c>
@@ -681,69 +699,63 @@
       <c r="E8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="10"/>
+      <c r="G8" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C9" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>50</v>
-      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="16"/>
       <c r="E9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="11"/>
+      <c r="F9" s="10"/>
       <c r="G9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="11" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="12"/>
-      <c r="D10" s="4" t="s">
-        <v>51</v>
-      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="10"/>
+      <c r="G10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="12"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="3:9" x14ac:dyDescent="0.25">
       <c r="E11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="7" t="s">
+      <c r="F11" s="10"/>
+      <c r="G11" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="11"/>
+      <c r="F12" s="10"/>
       <c r="G12" s="2" t="s">
         <v>29</v>
       </c>
@@ -752,7 +764,7 @@
       <c r="E13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="11"/>
+      <c r="F13" s="10"/>
       <c r="G13" s="2" t="s">
         <v>25</v>
       </c>
@@ -761,7 +773,7 @@
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="10"/>
       <c r="G14" s="2" t="s">
         <v>24</v>
       </c>
@@ -770,157 +782,179 @@
       <c r="E15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="11"/>
+      <c r="F15" s="10"/>
       <c r="G15" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E16" s="2" t="s">
+      <c r="C16" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="11"/>
+      <c r="F16" s="10"/>
       <c r="G16" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C17" s="4" t="s">
-        <v>56</v>
-      </c>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C17" s="15"/>
       <c r="D17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="11"/>
+      <c r="F17" s="10"/>
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="E18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="11"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="E19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="11"/>
+      <c r="F19" s="10"/>
       <c r="G19" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="11"/>
+      <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C21" s="16" t="s">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C21" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="8" t="s">
+      <c r="F21" s="10"/>
+      <c r="G21" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C22" s="12"/>
-      <c r="D22" s="8" t="s">
+      <c r="J21" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C22" s="11"/>
+      <c r="D22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="11"/>
+      <c r="F22" s="10"/>
       <c r="G22" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I22" s="12"/>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C23" s="12"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C23" s="11"/>
       <c r="D23" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="11"/>
+      <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="E24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="11"/>
+      <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="11"/>
+      <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E26" s="15" t="s">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="E26" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="14" t="s">
+      <c r="F26" s="10"/>
+      <c r="G26" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E27" s="14" t="s">
+    <row r="27" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="E27" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="14" t="s">
+      <c r="F27" s="10"/>
+      <c r="G27" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="F29" s="1" t="s">
+    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F29" s="2" t="s">
         <v>55</v>
       </c>
     </row>
@@ -930,7 +964,7 @@
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C16:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
